--- a/output/2026-09-13_11_Croazia_Koprivnicko-krizevacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-13_11_Croazia_Koprivnicko-krizevacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
